--- a/Assets/Excel/SynergyEffectSO.xlsx
+++ b/Assets/Excel/SynergyEffectSO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8066B3-81FF-47EC-9340-83CD2DD8DCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB507CB-28C8-48E4-9D20-D5F60354321F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,136 +53,2602 @@
     <t>Prism</t>
   </si>
   <si>
-    <t>왕국 유닛의 체력 +10%</t>
-  </si>
-  <si>
     <t>Empire</t>
   </si>
   <si>
-    <t>황국 유닛의 코스트 -5%</t>
+    <t>Mage</t>
+  </si>
+  <si>
+    <t>Cleric</t>
+  </si>
+  <si>
+    <t>Berserker</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>Frost</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초 증가</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>황국 유닛의 코스트 -10%</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초 증가</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>황국 유닛의 코스트 -15%</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초 증가</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Mage</t>
-  </si>
-  <si>
-    <t>속성 효과 시간 1초 증가</t>
-  </si>
-  <si>
-    <t>속성 효과 시간 2초 증가</t>
-  </si>
-  <si>
-    <t>속성 효과 시간 3초 증가</t>
-  </si>
-  <si>
-    <t>모든 아군이 받는 회복량 +5%</t>
-  </si>
-  <si>
-    <t>버서커 유닛의 체력이 50% 이하일 때 공격 쿨타임 -20%</t>
-  </si>
-  <si>
-    <t>버서커 유닛의 체력이 50% 이하일 때 공격 쿨타임 -50%</t>
-  </si>
-  <si>
-    <t>Cleric</t>
-  </si>
-  <si>
-    <t>Berserker</t>
-  </si>
-  <si>
-    <t>궁수 유닛의 공격 쿨타임 10% 감소</t>
-  </si>
-  <si>
-    <t>궁수 유닛의 공격 쿨타임 25% 감소</t>
-  </si>
-  <si>
-    <t>모든 영웅 유닛의 체력 및 공격력 +20%</t>
-  </si>
-  <si>
-    <t>모든 영웅 유닛의 체력 및 공격력 +45%</t>
-  </si>
-  <si>
-    <t>모든 영웅 유닛의 체력 및 공격력 +70%</t>
-  </si>
-  <si>
-    <t>냉기 유닛이 공격 시 둔화가 아니라 기절시킴</t>
-  </si>
-  <si>
-    <t>냉기 유닛이 공격 시 50% 확률로 적을 2초간 기절시킴</t>
-  </si>
-  <si>
-    <t>화상 상태의 적은 받는 회복량 50% 감소</t>
-  </si>
-  <si>
-    <t>화상 상태의 적은 받는 회복량 80% 감소</t>
-  </si>
-  <si>
-    <t>Archer</t>
-  </si>
-  <si>
-    <t>Hero</t>
-  </si>
-  <si>
-    <t>Frost</t>
-  </si>
-  <si>
-    <t>Burn</t>
-  </si>
-  <si>
-    <t>Poison</t>
-  </si>
-  <si>
-    <t>왕국 유닛의 체력 +15%
-5초마다 왕국 유닛의 체력을 2%씩 회복</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왕국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>모든 아군이 받는 회복량 +5%
-15초마다 무작위 아군 1명의 해로운 효과 제거</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왕국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+10%</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>모든 아군이 받는 회복량 +5%
-15초마다 무작위 아군 1명의 해로운 효과 제거
-성직자 유닛 사망 시 모든 아군 체력을 10% 회복</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왕국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">마다 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왕국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>씩 회복</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>냉기 유닛이 공격 시 30% 확률로 적을 1초간 둔화
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>황국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>코스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-5%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>황국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>코스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>황국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>코스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-15%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 아군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 아군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">초마다 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>무작위 아군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">명의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>해로운 효과 제거</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 아군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">초마다 무작위 아군 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">명의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>해로운 효과 제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>성직자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛 사망 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 아군 체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버서커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이하일 때 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-20%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버서커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이하일 때 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-50%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>궁수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>궁수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 영웅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력 및 공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+20%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 영웅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력 및 공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+45%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 영웅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력 및 공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+70%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>냉기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 적을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>둔화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 (둔화는 이동 속도, 공격 쿨타임을 느려지게 함)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>화상 유닛이 공격 시 30% 확률로 대상을 5초간 화상 상태로 만듦
-화상 상태의 적은 회복량 25% 감소</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>냉기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>둔화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">가 아니라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시킴</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>왕국 유닛의 체력 +5%</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>냉기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 적을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시킴</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>중독 유닛이 공격 시 50% 확률로 대상을 5초간 중독 상태로 만듦</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 대상을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 상태로 만듦</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>중독 유닛이 공격 시 50% 확률로 대상을 5초간 중독 상태로 만듦
-중독 상태의 적이 사망할 경우 주변 유닛에게 전염
-( 중첩 1단계 )</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적은 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>80%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>중독 유닛이 공격 시 50% 확률로 대상을 5초간 중독 상태로 만듦
-중독 상태의 적이 사망할 경우 주변 유닛에게 전염
-( 죽은 유닛의 중첩 단계/2 )</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적은 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 대상을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 상태로 만듦
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상 상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 대상을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 상태로 만듦
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독 상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사망</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">할 경우 주변 유닛에게 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전염</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>( 죽은 유닛의 중첩 단계/2 )</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 대상을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 상태로 만듦
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독 상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사망</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">할 경우 주변 유닛에게 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전염</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>( 중첩 1단계 )</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -190,7 +2656,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +2666,66 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -226,9 +2752,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +3039,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
@@ -520,7 +3047,7 @@
     <col min="4" max="4" width="57.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +3061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>10000000</v>
       </c>
@@ -544,11 +3071,11 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>41</v>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>10000000</v>
       </c>
@@ -558,11 +3085,11 @@
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="33">
       <c r="A4">
         <v>10000000</v>
       </c>
@@ -572,358 +3099,358 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>36</v>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>10000000</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>10000000</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>10000000</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" t="s">
-        <v>12</v>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>10000000</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
-        <v>14</v>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>10000000</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
-        <v>15</v>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>10000000</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" t="s">
-        <v>16</v>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>10000000</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" t="s">
-        <v>17</v>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="33">
       <c r="A12">
         <v>10000000</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>37</v>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="49.5">
       <c r="A13">
         <v>10000000</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>38</v>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>10000000</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
-        <v>18</v>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>10000000</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
-      <c r="D15" t="s">
-        <v>19</v>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>10000000</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="D16" t="s">
-        <v>22</v>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>10000000</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17" t="s">
-        <v>23</v>
+      <c r="D17" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>10000000</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="D18" t="s">
-        <v>24</v>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>10000000</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
       </c>
-      <c r="D19" t="s">
-        <v>25</v>
+      <c r="D19" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>10000000</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" t="s">
-        <v>26</v>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="33">
       <c r="A21">
         <v>10000000</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>39</v>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>10000000</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
       </c>
-      <c r="D22" t="s">
-        <v>27</v>
+      <c r="D22" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>10000000</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
-      <c r="D23" t="s">
-        <v>28</v>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="33">
       <c r="A24">
         <v>10000000</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>40</v>
+      <c r="D24" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>10000000</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
       </c>
-      <c r="D25" t="s">
-        <v>29</v>
+      <c r="D25" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>10000000</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
-      <c r="D26" t="s">
-        <v>30</v>
+      <c r="D26" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>10000000</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
       </c>
-      <c r="D27" t="s">
-        <v>42</v>
+      <c r="D27" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="49.5">
       <c r="A28">
         <v>10000000</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>43</v>
+      <c r="D28" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="49.5">
       <c r="A29">
         <v>10000000</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>44</v>
+      <c r="D29" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/SynergyEffectSO.xlsx
+++ b/Assets/Excel/SynergyEffectSO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB507CB-28C8-48E4-9D20-D5F60354321F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D56F2CD-07C7-4592-BEED-35297E599609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>idNumber</t>
   </si>
@@ -2650,6 +2650,9 @@
       <t>( 중첩 1단계 )</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>requiredUnitCount</t>
   </si>
 </sst>
 </file>
@@ -3038,16 +3041,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="14.25" customWidth="1"/>
     <col min="4" max="4" width="57.625" customWidth="1"/>
+    <col min="5" max="5" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3060,8 +3064,11 @@
       <c r="D1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>10000000</v>
       </c>
@@ -3074,8 +3081,11 @@
       <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>10000000</v>
       </c>
@@ -3088,8 +3098,11 @@
       <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="33">
+    <row r="4" spans="1:5" ht="33">
       <c r="A4">
         <v>10000000</v>
       </c>
@@ -3102,8 +3115,11 @@
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>10000000</v>
       </c>
@@ -3116,8 +3132,11 @@
       <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>10000000</v>
       </c>
@@ -3130,8 +3149,11 @@
       <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>10000000</v>
       </c>
@@ -3144,8 +3166,11 @@
       <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>10000000</v>
       </c>
@@ -3158,8 +3183,11 @@
       <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>10000000</v>
       </c>
@@ -3172,8 +3200,11 @@
       <c r="D9" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>10000000</v>
       </c>
@@ -3186,8 +3217,11 @@
       <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10000000</v>
       </c>
@@ -3200,8 +3234,11 @@
       <c r="D11" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="1:4" ht="33">
+    <row r="12" spans="1:5" ht="33">
       <c r="A12">
         <v>10000000</v>
       </c>
@@ -3214,8 +3251,11 @@
       <c r="D12" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:4" ht="49.5">
+    <row r="13" spans="1:5" ht="49.5">
       <c r="A13">
         <v>10000000</v>
       </c>
@@ -3228,8 +3268,11 @@
       <c r="D13" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>10000000</v>
       </c>
@@ -3242,8 +3285,11 @@
       <c r="D14" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>10000000</v>
       </c>
@@ -3256,8 +3302,11 @@
       <c r="D15" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>10000000</v>
       </c>
@@ -3270,8 +3319,11 @@
       <c r="D16" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>10000000</v>
       </c>
@@ -3284,8 +3336,11 @@
       <c r="D17" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>10000000</v>
       </c>
@@ -3298,8 +3353,11 @@
       <c r="D18" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>10000000</v>
       </c>
@@ -3312,8 +3370,11 @@
       <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>10000000</v>
       </c>
@@ -3326,8 +3387,11 @@
       <c r="D20" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
     </row>
-    <row r="21" spans="1:4" ht="33">
+    <row r="21" spans="1:5" ht="33">
       <c r="A21">
         <v>10000000</v>
       </c>
@@ -3340,8 +3404,11 @@
       <c r="D21" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>10000000</v>
       </c>
@@ -3354,8 +3421,11 @@
       <c r="D22" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>10000000</v>
       </c>
@@ -3368,8 +3438,11 @@
       <c r="D23" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
     </row>
-    <row r="24" spans="1:4" ht="33">
+    <row r="24" spans="1:5" ht="33">
       <c r="A24">
         <v>10000000</v>
       </c>
@@ -3382,8 +3455,11 @@
       <c r="D24" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>10000000</v>
       </c>
@@ -3396,8 +3472,11 @@
       <c r="D25" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>10000000</v>
       </c>
@@ -3410,8 +3489,11 @@
       <c r="D26" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>10000000</v>
       </c>
@@ -3424,8 +3506,11 @@
       <c r="D27" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:4" ht="49.5">
+    <row r="28" spans="1:5" ht="49.5">
       <c r="A28">
         <v>10000000</v>
       </c>
@@ -3438,8 +3523,11 @@
       <c r="D28" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="1:4" ht="49.5">
+    <row r="29" spans="1:5" ht="49.5">
       <c r="A29">
         <v>10000000</v>
       </c>
@@ -3451,6 +3539,9 @@
       </c>
       <c r="D29" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="E29">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/SynergyEffectSO.xlsx
+++ b/Assets/Excel/SynergyEffectSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D56F2CD-07C7-4592-BEED-35297E599609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE3E7A7-2FA6-491D-906E-3FF5ADEDB41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,53 +184,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>속성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 효과 시간 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>초 증가</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>왕국</t>
     </r>
     <r>
@@ -1154,109 +1107,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이하일 때 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공격 쿨타임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-20%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>버서커</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color rgb="FF7030A0"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
@@ -2653,6 +2503,157 @@
   </si>
   <si>
     <t>requiredUnitCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 &lt;color=#E4FF00&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초 증가</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버서커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">50%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이하일 때 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-20%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3065,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3079,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3096,7 +3097,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -3113,7 +3114,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -3130,7 +3131,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3147,7 +3148,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -3164,7 +3165,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -3215,7 +3216,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -3232,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3249,7 +3250,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -3266,13 +3267,13 @@
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="33">
       <c r="A14">
         <v>10000000</v>
       </c>
@@ -3282,8 +3283,8 @@
       <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -3300,7 +3301,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -3317,7 +3318,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -3334,7 +3335,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -3351,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -3368,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -3385,7 +3386,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -3402,7 +3403,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -3419,7 +3420,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -3436,7 +3437,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -3453,7 +3454,7 @@
         <v>5</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -3470,7 +3471,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -3487,7 +3488,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -3504,7 +3505,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -3521,7 +3522,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -3538,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E29">
         <v>5</v>

--- a/Assets/Excel/SynergyEffectSO.xlsx
+++ b/Assets/Excel/SynergyEffectSO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE3E7A7-2FA6-491D-906E-3FF5ADEDB41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3F54C3-A2F9-4DAC-8851-F66043537EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="61">
   <si>
     <t>idNumber</t>
   </si>
@@ -2653,6 +2653,64 @@
       </rPr>
       <t>-20%</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synergyTypeText</t>
+  </si>
+  <si>
+    <t>synergyGradeText</t>
+  </si>
+  <si>
+    <t>왕국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성직자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버서커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중독</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브론즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리즘</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3042,17 +3100,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="14.25" customWidth="1"/>
     <col min="4" max="4" width="57.625" customWidth="1"/>
-    <col min="5" max="5" width="21.125" customWidth="1"/>
+    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="37.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3068,8 +3128,14 @@
       <c r="E1" t="s">
         <v>43</v>
       </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>10000000</v>
       </c>
@@ -3085,8 +3151,14 @@
       <c r="E2">
         <v>2</v>
       </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>10000000</v>
       </c>
@@ -3102,8 +3174,14 @@
       <c r="E3">
         <v>4</v>
       </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="33">
+    <row r="4" spans="1:7" ht="33">
       <c r="A4">
         <v>10000000</v>
       </c>
@@ -3119,8 +3197,14 @@
       <c r="E4">
         <v>6</v>
       </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>10000000</v>
       </c>
@@ -3136,8 +3220,14 @@
       <c r="E5">
         <v>2</v>
       </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>10000000</v>
       </c>
@@ -3153,8 +3243,14 @@
       <c r="E6">
         <v>4</v>
       </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>10000000</v>
       </c>
@@ -3170,8 +3266,14 @@
       <c r="E7">
         <v>6</v>
       </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>10000000</v>
       </c>
@@ -3187,8 +3289,14 @@
       <c r="E8">
         <v>2</v>
       </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>10000000</v>
       </c>
@@ -3204,8 +3312,14 @@
       <c r="E9">
         <v>4</v>
       </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>10000000</v>
       </c>
@@ -3221,8 +3335,14 @@
       <c r="E10">
         <v>6</v>
       </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10000000</v>
       </c>
@@ -3238,8 +3358,14 @@
       <c r="E11">
         <v>3</v>
       </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" ht="33">
+    <row r="12" spans="1:7" ht="33">
       <c r="A12">
         <v>10000000</v>
       </c>
@@ -3255,8 +3381,14 @@
       <c r="E12">
         <v>4</v>
       </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="13" spans="1:5" ht="49.5">
+    <row r="13" spans="1:7" ht="49.5">
       <c r="A13">
         <v>10000000</v>
       </c>
@@ -3272,8 +3404,14 @@
       <c r="E13">
         <v>5</v>
       </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="14" spans="1:5" ht="33">
+    <row r="14" spans="1:7" ht="33">
       <c r="A14">
         <v>10000000</v>
       </c>
@@ -3289,8 +3427,14 @@
       <c r="E14">
         <v>3</v>
       </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>10000000</v>
       </c>
@@ -3306,8 +3450,14 @@
       <c r="E15">
         <v>5</v>
       </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>10000000</v>
       </c>
@@ -3323,8 +3473,14 @@
       <c r="E16">
         <v>3</v>
       </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>10000000</v>
       </c>
@@ -3340,8 +3496,14 @@
       <c r="E17">
         <v>5</v>
       </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>10000000</v>
       </c>
@@ -3357,8 +3519,14 @@
       <c r="E18">
         <v>2</v>
       </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>10000000</v>
       </c>
@@ -3374,8 +3542,14 @@
       <c r="E19">
         <v>4</v>
       </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>10000000</v>
       </c>
@@ -3391,8 +3565,14 @@
       <c r="E20">
         <v>6</v>
       </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="21" spans="1:5" ht="33">
+    <row r="21" spans="1:7" ht="33">
       <c r="A21">
         <v>10000000</v>
       </c>
@@ -3408,8 +3588,14 @@
       <c r="E21">
         <v>2</v>
       </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>10000000</v>
       </c>
@@ -3425,8 +3611,14 @@
       <c r="E22">
         <v>3</v>
       </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>10000000</v>
       </c>
@@ -3442,8 +3634,14 @@
       <c r="E23">
         <v>5</v>
       </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" ht="33">
+    <row r="24" spans="1:7" ht="33">
       <c r="A24">
         <v>10000000</v>
       </c>
@@ -3459,8 +3657,14 @@
       <c r="E24">
         <v>1</v>
       </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>10000000</v>
       </c>
@@ -3476,8 +3680,14 @@
       <c r="E25">
         <v>2</v>
       </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>10000000</v>
       </c>
@@ -3493,8 +3703,14 @@
       <c r="E26">
         <v>3</v>
       </c>
+      <c r="F26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>10000000</v>
       </c>
@@ -3510,8 +3726,14 @@
       <c r="E27">
         <v>2</v>
       </c>
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="28" spans="1:5" ht="49.5">
+    <row r="28" spans="1:7" ht="49.5">
       <c r="A28">
         <v>10000000</v>
       </c>
@@ -3527,8 +3749,14 @@
       <c r="E28">
         <v>3</v>
       </c>
+      <c r="F28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="29" spans="1:5" ht="49.5">
+    <row r="29" spans="1:7" ht="49.5">
       <c r="A29">
         <v>10000000</v>
       </c>
@@ -3543,6 +3771,12 @@
       </c>
       <c r="E29">
         <v>5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/SynergyEffectSO.xlsx
+++ b/Assets/Excel/SynergyEffectSO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3F54C3-A2F9-4DAC-8851-F66043537EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F904E37D-A273-445B-9805-B4DAB51911C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,27 +80,180 @@
     <t>Poison</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>속성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 효과 시간 </t>
+    <t>requiredUnitCount</t>
+  </si>
+  <si>
+    <t>synergyTypeText</t>
+  </si>
+  <si>
+    <t>synergyGradeText</t>
+  </si>
+  <si>
+    <t>왕국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성직자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버서커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중독</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브론즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리즘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왕국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왕국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -112,64 +265,18 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>초 증가</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>속성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 효과 시간 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>초 증가</t>
+      <t>+5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -216,125 +323,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+5%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왕국</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+10%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왕국</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -347,6 +336,17 @@
         <scheme val="minor"/>
       </rPr>
       <t>+15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -369,17 +369,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>초</t>
+      <t>&lt;color=#A3FFF6&gt;5초&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -433,7 +423,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">을 </t>
+      <t>을 &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -445,7 +435,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2%</t>
+      <t>2%&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -502,7 +492,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -516,6 +506,17 @@
       </rPr>
       <t>-5%</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -561,7 +562,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
     </r>
     <r>
       <rPr>
@@ -575,6 +576,17 @@
       </rPr>
       <t>-10%</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -620,7 +632,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -634,6 +646,158 @@
       </rPr>
       <t>-15%</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 &lt;color=#4472C4&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초&lt;/color&gt;증가</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초&lt;/color&gt; 증가</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 효과 시간 &lt;color=#A3FFF6&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초&lt;/color&gt; 증가</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -679,7 +843,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -693,6 +857,17 @@
       </rPr>
       <t>+5%</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -738,7 +913,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
     </r>
     <r>
       <rPr>
@@ -750,7 +925,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>+5%</t>
+      <t>+5%&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -773,17 +948,17 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">초마다 </t>
+      <t>&lt;color=#7030A0&gt;15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">초&lt;/color&gt;마다 </t>
     </r>
     <r>
       <rPr>
@@ -886,7 +1061,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -898,7 +1073,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>+5%</t>
+      <t>+5%&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -921,17 +1096,17 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">초마다 무작위 아군 </t>
+      <t>&lt;color=#A3FFF6&gt;15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초&lt;/color&gt;마다 무작위 아군 &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -953,7 +1128,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">명의 </t>
+      <t xml:space="preserve">명&lt;/color&gt;의 </t>
     </r>
     <r>
       <rPr>
@@ -1020,7 +1195,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">을 </t>
+      <t>을 &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1032,7 +1207,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>10%</t>
+      <t>10%&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1101,7 +1276,111 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">이 </t>
+      <t>이 &lt;color=#4472C4&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">50%&lt;/color&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이하일 때 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-20%&lt;/color&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버서커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이 &lt;color=#7030A0&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1113,17 +1392,18 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이하일 때 </t>
+      <t xml:space="preserve">50%&lt;/color&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이하일 때 </t>
     </r>
     <r>
       <rPr>
@@ -1145,7 +1425,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1157,7 +1437,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>-50%</t>
+      <t>-50%&lt;/color&gt;</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1204,7 +1484,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1216,7 +1496,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>10%</t>
+      <t>10%&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1241,7 +1521,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>궁수</t>
+      <t>모든 영웅</t>
     </r>
     <r>
       <rPr>
@@ -1263,75 +1543,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>공격 쿨타임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>25%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 감소</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>모든 영웅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>체력 및 공격력</t>
     </r>
     <r>
@@ -1342,7 +1553,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1356,123 +1567,16 @@
       </rPr>
       <t>+20%</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>모든 영웅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력 및 공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+45%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>모든 영웅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력 및 공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+70%</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1497,7 +1601,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 유닛이 공격 시 </t>
+      <t xml:space="preserve"> 유닛이 공격 시 &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1509,17 +1613,17 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 확률로 적을 </t>
+      <t>30%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 적을 &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1531,7 +1635,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1초</t>
+      <t>1초&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1579,6 +1683,145 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>궁수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공격 쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 영웅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력 및 공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+45%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>냉기</t>
     </r>
     <r>
@@ -1611,7 +1854,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">가 아니라 </t>
+      <t>가 아니라 &lt;color=#7030A0&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1623,6 +1866,258 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>기절&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시킴</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적은 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>모든 영웅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력 및 공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#A3FFF6&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+70%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>냉기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 &lt;color=#A3FFF6&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로 적을 &lt;color=#A3FFF6&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2초&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>기절</t>
     </r>
     <r>
@@ -1648,17 +2143,61 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>냉기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛이 공격 시 </t>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">의 적은 받는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;color=#A3FFF6&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1670,86 +2209,42 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 확률로 적을 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2초</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">간 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>기절</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시킴</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>중독</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛이 공격 시 </t>
+      <t>80%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 감소</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1761,17 +2256,18 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 확률로 대상을 </t>
+      <t>30%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로
+대상을 &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -1783,280 +2279,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>5초</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">간 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>중독</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 상태로 만듦</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>화상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">의 적은 받는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>회복량</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>80%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 감소</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>화상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">의 적은 받는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>회복량</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 감소</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>화상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛이 공격 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 확률로 대상을 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5초</t>
+      <t>5초&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -2133,7 +2356,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> &lt;color=#4472C4&gt;</t>
     </r>
     <r>
       <rPr>
@@ -2145,7 +2368,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>25%</t>
+      <t>25%&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -2180,41 +2403,134 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 유닛이 공격 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 확률로 대상을 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="7"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5초</t>
+      <t xml:space="preserve"> 유닛이 공격 시 &lt;color=#4472C4&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로
+대상을 &lt;color=#4472C4&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">간 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 상태로 만듦</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50%&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 확률로
+대상을 &lt;color=#7030A0&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -2320,49 +2636,49 @@
       <rPr>
         <b/>
         <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;color=#7030A0&gt;( 중첩 1단계 )&lt;/color&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중독</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유닛이 공격 시 &lt;color=#A3FFF6&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <color theme="7"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>( 죽은 유닛의 중첩 단계/2 )</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>중독</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛이 공격 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>50%</t>
     </r>
     <r>
@@ -2373,19 +2689,20 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 확률로 대상을 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5초</t>
+      <t xml:space="preserve"> 확률로
+대상을 &lt;color=#A3FFF6&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5초&lt;/color&gt;</t>
     </r>
     <r>
       <rPr>
@@ -2491,226 +2808,25 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>( 중첩 1단계 )</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>requiredUnitCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>속성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 효과 시간 &lt;color=#E4FF00&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3&lt;/color&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>초 증가</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>버서커</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유닛의 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">50%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이하일 때 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공격 쿨타임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-20%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>synergyTypeText</t>
-  </si>
-  <si>
-    <t>synergyGradeText</t>
-  </si>
-  <si>
-    <t>왕국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>성직자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>버서커</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>궁수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중독</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>브론즈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리즘</t>
+        <color theme="7"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;color=#A3FFF6&gt;( 죽은 유닛의 중첩 단계/2 )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2718,7 +2834,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2771,13 +2887,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -2816,8 +2925,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3101,18 +3210,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="14.25" customWidth="1"/>
-    <col min="4" max="4" width="57.625" customWidth="1"/>
+    <col min="4" max="4" width="103" customWidth="1"/>
     <col min="5" max="5" width="19.625" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="37.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3126,16 +3235,16 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10000000</v>
       </c>
@@ -3146,19 +3255,19 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10000000</v>
       </c>
@@ -3169,19 +3278,19 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="33">
+    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>10000000</v>
       </c>
@@ -3192,19 +3301,19 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>10000000</v>
       </c>
@@ -3215,19 +3324,19 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10000000</v>
       </c>
@@ -3238,19 +3347,19 @@
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>10000000</v>
       </c>
@@ -3261,19 +3370,19 @@
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10000000</v>
       </c>
@@ -3284,19 +3393,19 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>10000000</v>
       </c>
@@ -3307,19 +3416,19 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E9">
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10000000</v>
       </c>
@@ -3330,19 +3439,19 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10000000</v>
       </c>
@@ -3353,19 +3462,19 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="33">
+    <row r="12" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10000000</v>
       </c>
@@ -3376,19 +3485,19 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="49.5">
+    <row r="13" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10000000</v>
       </c>
@@ -3399,19 +3508,19 @@
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="33">
+    <row r="14" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>10000000</v>
       </c>
@@ -3428,13 +3537,13 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>10000000</v>
       </c>
@@ -3444,20 +3553,20 @@
       <c r="C15" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>28</v>
+      <c r="D15" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>10000000</v>
       </c>
@@ -3468,19 +3577,19 @@
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>10000000</v>
       </c>
@@ -3491,19 +3600,19 @@
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>10000000</v>
       </c>
@@ -3514,19 +3623,19 @@
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>10000000</v>
       </c>
@@ -3537,19 +3646,19 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E19">
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>10000000</v>
       </c>
@@ -3560,19 +3669,19 @@
         <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E20">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="33">
+    <row r="21" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>10000000</v>
       </c>
@@ -3583,19 +3692,19 @@
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>10000000</v>
       </c>
@@ -3606,19 +3715,19 @@
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>10000000</v>
       </c>
@@ -3629,19 +3738,19 @@
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E23">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="33">
+    <row r="24" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>10000000</v>
       </c>
@@ -3652,19 +3761,19 @@
         <v>5</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>10000000</v>
       </c>
@@ -3675,19 +3784,19 @@
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>10000000</v>
       </c>
@@ -3698,19 +3807,19 @@
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>10000000</v>
       </c>
@@ -3720,20 +3829,20 @@
       <c r="C27" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>37</v>
+      <c r="D27" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="49.5">
+    <row r="28" spans="1:7" ht="66" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>10000000</v>
       </c>
@@ -3744,19 +3853,19 @@
         <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="49.5">
+    <row r="29" spans="1:7" ht="66" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>10000000</v>
       </c>
@@ -3767,16 +3876,16 @@
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E29">
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/SynergyEffectSO.xlsx
+++ b/Assets/Excel/SynergyEffectSO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F904E37D-A273-445B-9805-B4DAB51911C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFAB0F7-8ADB-4966-A3F5-0CEE0ADB9730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3764,7 +3764,7 @@
         <v>57</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>53</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -3810,7 +3810,7 @@
         <v>56</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
